--- a/public/downloads/goldfin-expense-and-vendor-audit-sample.xlsx
+++ b/public/downloads/goldfin-expense-and-vendor-audit-sample.xlsx
@@ -18,8 +18,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0;[Red]($#,##0);-"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot; mo&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
   <fonts count="6">
@@ -189,7 +189,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -212,7 +212,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="8">
@@ -222,7 +222,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="9">
@@ -232,7 +232,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <v>-41180</v>
+        <v>-71900</v>
       </c>
     </row>
     <row r="10">
@@ -242,7 +242,7 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="11">
@@ -313,7 +313,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 to 2026-05-31</t>
+          <t>2026-05-01 to 2026-05-31</t>
         </is>
       </c>
     </row>
@@ -344,7 +344,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>-41180</v>
+        <v>-71900</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B4" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="5">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="6">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>41180</v>
+        <v>71900</v>
       </c>
     </row>
     <row r="7">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="8">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>6800</v>
+        <v>72948</v>
       </c>
     </row>
     <row r="9">
@@ -694,8 +694,8 @@
           <t>runwayMonths</t>
         </is>
       </c>
-      <c r="B9" s="8">
-        <v>5.6</v>
+      <c r="B9" s="11">
+        <v>3.67</v>
       </c>
     </row>
     <row r="10">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <v>14600</v>
+        <v>22700</v>
       </c>
     </row>
     <row r="11">
@@ -714,7 +714,7 @@
           <t>revenueVsPriorPct</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="10">
         <v>6.4</v>
       </c>
     </row>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="13">
@@ -734,7 +734,7 @@
           <t>profitVsPriorPct</t>
         </is>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="10">
         <v>3.1</v>
       </c>
     </row>
@@ -754,7 +754,7 @@
           <t>coveragePct</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="10">
         <v>94</v>
       </c>
     </row>
@@ -764,7 +764,7 @@
           <t>transactionsCount</t>
         </is>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="12">
         <v>118</v>
       </c>
     </row>
@@ -774,7 +774,7 @@
           <t>reserve_floor_months</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="12">
         <v>3</v>
       </c>
     </row>
@@ -792,7 +792,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Detail</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
@@ -804,12 +804,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Not embedded</t>
+          <t>Transaction detail</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>The current frontend report snapshot does not include raw transaction rows. Server-side XLSX generation can populate this sheet from the transactions table.</t>
+          <t>This planning workbook summarizes your connected bank and card activity. Line-item transaction detail lives in your GoldFin Desk account and your own bank export.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/goldfin-expense-and-vendor-audit-sample.xlsx
+++ b/public/downloads/goldfin-expense-and-vendor-audit-sample.xlsx
@@ -217,7 +217,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Sample figures</t>
+          <t>Sample figures (pre-filled - type over them)</t>
         </is>
       </c>
     </row>
@@ -251,16 +251,36 @@
         <v>71900</v>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Profit this month</t>
+        </is>
+      </c>
+      <c r="B14" s="8">
+        <v>24500</v>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Profit margin</t>
+        </is>
+      </c>
+      <c r="B15" s="10">
+        <v>25.41</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Prefer it filled from your bank every month? That is GoldFin Reports - goldfindesk.com/pricing</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>A planning artifact, not tax, accounting, credit, legal, or investment advice.</t>
         </is>
@@ -273,8 +293,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -305,7 +328,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>List your recurring vendors and their monthly cost in the shaded cells. Totals update automatically; add rows as needed.</t>
+          <t>List each recurring vendor, its monthly cost, and whether to Keep, Review, or Cut it. Totals and savings update as you edit.</t>
         </is>
       </c>
     </row>
@@ -313,7 +336,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Recurring vendors</t>
+          <t>Recurring vendors (edit these)</t>
         </is>
       </c>
     </row>
@@ -325,7 +348,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Monthly cost</t>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>% of total</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Keep / Review / Cut</t>
         </is>
       </c>
     </row>
@@ -338,6 +376,19 @@
       <c r="B8" s="14">
         <v>49</v>
       </c>
+      <c r="C8" s="8">
+        <f>B8*12</f>
+        <v>588</v>
+      </c>
+      <c r="D8" s="10">
+        <f>IF($B$14=0,0,B8/$B$14*100)</f>
+        <v>10.02</v>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
@@ -348,6 +399,19 @@
       <c r="B9" s="14">
         <v>30</v>
       </c>
+      <c r="C9" s="8">
+        <f>B9*12</f>
+        <v>360</v>
+      </c>
+      <c r="D9" s="10">
+        <f>IF($B$14=0,0,B9/$B$14*100)</f>
+        <v>6.13</v>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
@@ -358,6 +422,19 @@
       <c r="B10" s="14">
         <v>410</v>
       </c>
+      <c r="C10" s="8">
+        <f>B10*12</f>
+        <v>4920</v>
+      </c>
+      <c r="D10" s="10">
+        <f>IF($B$14=0,0,B10/$B$14*100)</f>
+        <v>83.84</v>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -368,6 +445,19 @@
       <c r="B11" s="14">
         <v>0</v>
       </c>
+      <c r="C11" s="8">
+        <f>B11*12</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="10">
+        <f>IF($B$14=0,0,B11/$B$14*100)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
@@ -378,6 +468,19 @@
       <c r="B12" s="14">
         <v>0</v>
       </c>
+      <c r="C12" s="8">
+        <f>B12*12</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="10">
+        <f>IF($B$14=0,0,B12/$B$14*100)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -388,35 +491,70 @@
       <c r="B13" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Totals</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Total monthly recurring</t>
-        </is>
-      </c>
-      <c r="B16" s="9">
+      <c r="C13" s="8">
+        <f>B13*12</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="10">
+        <f>IF($B$14=0,0,B13/$B$14*100)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
         <f>SUM(B8:B13)</f>
         <v>489</v>
       </c>
+      <c r="C14" s="8">
+        <f>SUM(C8:C13)</f>
+        <v>5868</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Your savings opportunity</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Annualized</t>
+          <t>Monthly cost of vendors marked Cut</t>
         </is>
       </c>
       <c r="B17" s="8">
-        <f>SUM(B8:B13)*12</f>
-        <v>5868</v>
+        <f>SUMIF(E8:E13,"Cut",B8:B13)</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Annual savings if you cut them</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>SUMIF(E8:E13,"Cut",C8:C13)</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="13" t="str">
+        <f>IF(SUMIF(E8:E13,"Cut",C8:C13)&gt;0,"Cutting the vendors you marked Cut saves the annual amount above","Mark any vendor Cut to see the annual savings")</f>
+        <v>Cutting the vendors you marked Cut saves the annual amount above</v>
       </c>
     </row>
   </sheetData>
